--- a/SGC-CKN/Excel/9b05a8d1-b46f-4040-89d1-db2a912d9608_Lô_CT-02_P1-167_D800_24-03-2026.xlsx
+++ b/SGC-CKN/Excel/9b05a8d1-b46f-4040-89d1-db2a912d9608_Lô_CT-02_P1-167_D800_24-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
   <si>
     <t>Dự án</t>
   </si>
@@ -115,7 +115,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">18:15
+    <t xml:space="preserve">18:10
 23/03/2026</t>
   </si>
   <si>
@@ -123,16 +123,20 @@
   </si>
   <si>
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:30
+23/03/2026</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">18:35
 23/03/2026</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">22:00
@@ -1219,13 +1223,13 @@
         <v>-4.1</v>
       </c>
       <c r="H12" s="9">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="9">
         <v>0.8</v>
       </c>
       <c r="J12" s="12">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1277,10 +1281,10 @@
         <v>38</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="16">
         <v>-7.6</v>
@@ -1303,19 +1307,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="20">
         <v>-10.8</v>
@@ -1338,19 +1342,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" s="23">
         <v>-19.7</v>
@@ -1373,19 +1377,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17" s="26">
         <v>-25</v>
@@ -1403,24 +1407,24 @@
         <v>14</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" s="29">
         <v>-39</v>
@@ -1443,7 +1447,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -1549,31 +1553,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1625,13 +1629,13 @@
         <v>-4.1</v>
       </c>
       <c r="G3" s="9">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="H3" s="9">
         <v>0.8</v>
       </c>
       <c r="I3" s="12">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1700,7 +1704,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="20">
         <v>1</v>
@@ -1729,7 +1733,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="23">
         <v>1</v>
@@ -1758,7 +1762,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
@@ -1787,7 +1791,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="29">
         <v>1</v>
@@ -1810,7 +1814,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>30</v>
@@ -1828,13 +1832,13 @@
         <v>-44.2</v>
       </c>
       <c r="G10" s="34">
-        <v>10.97</v>
+        <v>10.88</v>
       </c>
       <c r="H10" s="34">
         <v>44.2</v>
       </c>
       <c r="I10" s="34">
-        <v>4.03</v>
+        <v>4.06</v>
       </c>
     </row>
   </sheetData>
